--- a/assets/factor/practice/Regression Questions - ANOVA Problem Set 4.xlsx
+++ b/assets/factor/practice/Regression Questions - ANOVA Problem Set 4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\FIN 203\FIN 203 Fall 2020\4 Factor Models\3 Practice\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\FIN 203\FIN 203 Fall 2020\S3 Online\assets\factor\practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A691536-C15A-44BD-8951-B9DFBEC6F435}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87920AEF-70EC-43DA-9205-C0D5FEA32F33}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{8DCDFA2E-5CA9-465E-B789-4F49B614B1AD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{8DCDFA2E-5CA9-465E-B789-4F49B614B1AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Question" sheetId="10" r:id="rId1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="12">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="10"/>
